--- a/TestData/Withdraw_TestData.xlsx
+++ b/TestData/Withdraw_TestData.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.1796875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -507,11 +507,16 @@
           <t>WalletNumber</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ReceiveInformation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E-Wallet Withdraw</t>
+          <t>HKD withdraw to FPS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,8 +529,10 @@
           <t>12345678</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>100</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -552,22 +559,1281 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>65345678234</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>null</t>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>From Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PHP withdraw to its saved account</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SAVED</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>From Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BDT withdraw to USDT-TRC 20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BDT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>USDT-TRC 20</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>From Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MXN withdraw to AFIRME</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AFIRME</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>From Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BRL withdraw to its saved account</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SAVED</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>From Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VND withdraw to its saved account</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SAVED</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>From Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IDR withdraw to DANA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DANA</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>From Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>THB withdraw to Bangkok Bank</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bangkok Bank Plc.</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>From Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MYR withdraw to its saved account</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SAVED</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>From Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>USD withdraw to USDT-TRC 20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>USDT-TRC 20</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>From Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HKD withdraw to a new FPS account</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FPS</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>New Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PHP withdraw to a new bank account</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GLOBE GCASH</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>New Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BDT withdraw to a new USDT address</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BDT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>USDT-TRC 20</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>TQn9Y2khDD95J42FQtQTdwVVRZqiL1zTNA</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>New Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MXN withdraw to a new bank account</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AFIRME</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>New Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BRL withdraw to a new CPF account</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CPF</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>52998224725</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>New Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VND withdraw to a new bank account</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vietcombank</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>New Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IDR withdraw to a new DANA account</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DANA</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>New Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>THB withdraw to a new bank account</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bangkok Bank Plc.</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>New Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MYR withdraw to a new account</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Duitnow</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>New Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>USD withdraw to a new USDT address</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>USDT-TRC 20</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>TQn9Y2khDD95J42FQtQTdwVVRZqiL1zTNA</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>New Account</t>
         </is>
       </c>
     </row>
